--- a/files/九龙-马头角-瑧博.xlsx
+++ b/files/九龙-马头角-瑧博.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="瑧博 销控表" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="瑧博" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,14 +44,19 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -63,7 +68,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -74,7 +79,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00002060"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -85,7 +90,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00660000"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -95,9 +100,30 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -170,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,19 +213,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,10 +231,34 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -598,7 +636,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -6197,141 +6235,141 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>瑧博 - 瑧博 销控网格图</t>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>瑧博 销控网格图</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>总套数</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>在售 (Sale)</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
         <is>
           <t>已定价未售</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>已售 (Sold)</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="11" t="inlineStr">
         <is>
           <t>暂停销售</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="12" t="inlineStr">
         <is>
           <t>待售 (Pending)</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>120 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>119 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G4" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,518万
+$1518万
 $25,015/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C5" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $927万
@@ -6339,7 +6377,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $618万
@@ -6347,7 +6385,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E6" s="16" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $847万
@@ -6355,15 +6393,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,812万
+$1812万
 $31,234/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G6" s="16" t="inlineStr">
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $400万
@@ -6372,21 +6410,21 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,233万
+$1233万
 $20,320/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C6" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $785万
@@ -6394,7 +6432,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $578万
@@ -6402,7 +6440,7 @@
 (25年-09月)</t>
         </is>
       </c>
-      <c r="E7" s="16" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $713万
@@ -6410,15 +6448,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,158万
+$1158万
 $19,969/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $424万
@@ -6427,21 +6465,21 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,358万
+$1358万
 $22,381/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $707万
@@ -6449,7 +6487,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $542万
@@ -6457,7 +6495,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E8" s="16" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $701万
@@ -6465,15 +6503,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F8" s="16" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,158万
+$1158万
 $19,967/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
+      <c r="G7" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $399万
@@ -6482,21 +6520,21 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,301万
+$1301万
 $21,427/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $700万
@@ -6504,7 +6542,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $566万
@@ -6512,7 +6550,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E9" s="16" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $689万
@@ -6520,15 +6558,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F9" s="16" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,129万
+$1129万
 $19,462/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G8" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $399万
@@ -6537,21 +6575,21 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,155万
+$1155万
 $19,025/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $762万
@@ -6559,7 +6597,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $561万
@@ -6567,7 +6605,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E10" s="16" t="inlineStr">
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $677万
@@ -6575,15 +6613,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F10" s="16" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,096万
+$1096万
 $18,897/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr">
+      <c r="G9" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $399万
@@ -6592,21 +6630,21 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,156万
+$1156万
 $19,041/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $686万
@@ -6614,7 +6652,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $504万
@@ -6622,7 +6660,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E11" s="16" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $663万
@@ -6630,15 +6668,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F11" s="16" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,080万
+$1080万
 $18,616/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G10" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $398万
@@ -6647,21 +6685,21 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,110万
+$1110万
 $18,287/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $678万
@@ -6669,7 +6707,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $548万
@@ -6677,7 +6715,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E12" s="16" t="inlineStr">
+      <c r="E11" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $639万
@@ -6685,15 +6723,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F12" s="16" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,034万
+$1034万
 $17,822/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G12" s="16" t="inlineStr">
+      <c r="G11" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $428万
@@ -6702,21 +6740,21 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,155万
+$1155万
 $19,026/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $737万
@@ -6724,7 +6762,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $488万
@@ -6732,7 +6770,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E13" s="16" t="inlineStr">
+      <c r="E12" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $635万
@@ -6740,15 +6778,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F13" s="16" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,008万
+$1008万
 $17,376/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G12" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $398万
@@ -6757,21 +6795,21 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,090万
+$1090万
 $17,951/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $722万
@@ -6779,7 +6817,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $446万
@@ -6787,7 +6825,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E14" s="16" t="inlineStr">
+      <c r="E13" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $630万
@@ -6795,7 +6833,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F14" s="16" t="inlineStr">
+      <c r="F13" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $996万
@@ -6803,7 +6841,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $427万
@@ -6812,21 +6850,21 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,096万
+$1096万
 $18,048/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $632万
@@ -6834,7 +6872,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $472万
@@ -6842,7 +6880,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E15" s="16" t="inlineStr">
+      <c r="E14" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $626万
@@ -6850,7 +6888,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F15" s="16" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $984万
@@ -6858,7 +6896,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G14" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $439万
@@ -6867,21 +6905,21 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,045万
+$1045万
 $17,216/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C16" s="16" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $635万
@@ -6889,7 +6927,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $468万
@@ -6897,7 +6935,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E16" s="16" t="inlineStr">
+      <c r="E15" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $683万
@@ -6905,7 +6943,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F16" s="16" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $990万
@@ -6913,7 +6951,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G15" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $426万
@@ -6922,21 +6960,21 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,065万
+$1065万
 $17,550/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C17" s="16" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $697万
@@ -6944,7 +6982,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $467万
@@ -6952,7 +6990,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
+      <c r="E16" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $618万
@@ -6960,7 +6998,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F17" s="16" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $985万
@@ -6968,7 +7006,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G16" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $426万
@@ -6977,21 +7015,21 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,044万
+$1044万
 $17,199/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C18" s="16" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $695万
@@ -6999,7 +7037,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $466万
@@ -7007,7 +7045,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E17" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $676万
@@ -7015,7 +7053,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $980万
@@ -7023,7 +7061,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G18" s="16" t="inlineStr">
+      <c r="G17" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $425万
@@ -7032,21 +7070,21 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,039万
+$1039万
 $17,114/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C19" s="16" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $630万
@@ -7054,7 +7092,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $511万
@@ -7062,7 +7100,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E18" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $673万
@@ -7070,7 +7108,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F19" s="16" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $975万
@@ -7078,7 +7116,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G18" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $425万
@@ -7087,21 +7125,21 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,034万
+$1034万
 $17,028/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C20" s="16" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $691万
@@ -7109,7 +7147,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $456万
@@ -7117,7 +7155,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E19" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $609万
@@ -7125,7 +7163,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $970万
@@ -7133,7 +7171,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G20" s="16" t="inlineStr">
+      <c r="G19" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $419万
@@ -7142,21 +7180,21 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,131万
+$1131万
 $18,638/呎
 (25年-09月)</t>
         </is>
       </c>
-      <c r="C21" s="16" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $609万
@@ -7164,7 +7202,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $454万
@@ -7172,7 +7210,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E20" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $606万
@@ -7180,7 +7218,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F21" s="16" t="inlineStr">
+      <c r="F20" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $962万
@@ -7188,7 +7226,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G20" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $411万
@@ -7197,21 +7235,21 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,023万
+$1023万
 $16,858/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C22" s="16" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $672万
@@ -7219,7 +7257,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $452万
@@ -7227,7 +7265,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E22" s="16" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $596万
@@ -7235,7 +7273,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F22" s="16" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $951万
@@ -7243,7 +7281,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G22" s="16" t="inlineStr">
+      <c r="G21" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $444万
@@ -7252,21 +7290,21 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
-$1,013万
+$1013万
 $16,689/呎
 (已售)</t>
         </is>
       </c>
-      <c r="C23" s="16" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $604万
@@ -7274,7 +7312,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $445万
@@ -7282,7 +7320,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E23" s="16" t="inlineStr">
+      <c r="E22" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $584万
@@ -7290,15 +7328,15 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F23" s="16" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
-$1,030万
+$1030万
 $17,767/呎
 (已售)</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G22" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $396万
@@ -7307,13 +7345,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
 $972万
@@ -7321,7 +7359,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C24" s="16" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $595万
@@ -7329,7 +7367,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $438万
@@ -7337,7 +7375,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E24" s="16" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $573万
@@ -7345,7 +7383,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F24" s="16" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $918万
@@ -7353,7 +7391,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G24" s="16" t="inlineStr">
+      <c r="G23" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $388万
@@ -7362,13 +7400,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 607呎 (3房)
 $954万
@@ -7376,7 +7414,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="C25" s="16" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 330呎 (2房)
 $584万
@@ -7384,7 +7422,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>C | 244呎 (1房)
 $429万
@@ -7392,7 +7430,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="E25" s="16" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>D | 335呎 (2房)
 $611万
@@ -7400,7 +7438,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="F25" s="16" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>E | 580呎 (3房)
 $900万
@@ -7408,7 +7446,7 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t>F | 252呎 (1房)
 $378万
@@ -7419,7 +7457,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
